--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M28B2_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M28B2_IN_Piura.xlsx
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>4.08</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>33.72</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C12" s="29">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>51.97</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>8.79</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>1.43</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1912,11 +1912,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>90.1974</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1937,11 +1937,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>34.1018</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>37.81</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1962,11 +1962,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>56.0956</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>62.19</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>90.2279</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2283,6 +2283,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2367,6 +2368,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2411,6 +2413,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="132" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2836,11 +2839,11 @@
       </c>
       <c r="B18" s="32">
         <f>SUM(B10:B17)</f>
-        <v/>
+        <v>484.3</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C10:C17)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -2850,19 +2853,19 @@
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17">
         <f>ROUND(AVERAGE(F10:F17),2)</f>
-        <v/>
+        <v>25.51</v>
       </c>
       <c r="G18" s="22">
         <f>ROUND(AVERAGE(G10:G17),4)</f>
-        <v/>
+        <v>0.6021</v>
       </c>
       <c r="H18" s="23">
         <f>ROUND(AVERAGE(H10:H17),2)</f>
-        <v/>
+        <v>66.1</v>
       </c>
       <c r="I18" s="23">
         <f>ROUND(AVERAGE(I10:I17),2)</f>
-        <v/>
+        <v>32.65</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
